--- a/final-plan/Final-Plan-Pose-List.xlsx
+++ b/final-plan/Final-Plan-Pose-List.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Who sees it free</t>
+          <t>Free to do?</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Yes, unlimited</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Yes, unlimited</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Yes, unlimited</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Yes, unlimited</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Yes, unlimited</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Yes, unlimited</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Yes, unlimited</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -612,10 +612,9 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -628,10 +627,9 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -644,10 +642,9 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -660,10 +657,9 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -676,10 +672,9 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -692,10 +687,9 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -708,10 +702,9 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -724,10 +717,9 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -740,10 +732,9 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -756,10 +747,9 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -772,10 +762,9 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -788,10 +777,9 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -804,10 +792,9 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -820,10 +807,9 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -836,10 +822,9 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -852,10 +837,9 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -868,10 +852,9 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -884,10 +867,9 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -900,10 +882,9 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -916,10 +897,9 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -932,10 +912,9 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -948,10 +927,9 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -964,10 +942,9 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -980,10 +957,9 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -996,10 +972,9 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1012,10 +987,9 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1028,10 +1002,9 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1044,10 +1017,9 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1060,10 +1032,9 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1076,10 +1047,9 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1092,10 +1062,9 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1108,10 +1077,9 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1124,10 +1092,9 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1140,10 +1107,9 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1156,10 +1122,9 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1172,10 +1137,9 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1188,10 +1152,9 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1204,10 +1167,9 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1220,10 +1182,9 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1236,10 +1197,9 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1252,10 +1212,9 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1268,10 +1227,9 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1284,10 +1242,9 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1300,10 +1257,9 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1316,10 +1272,9 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1332,10 +1287,9 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1348,10 +1302,9 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1364,10 +1317,9 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1380,10 +1332,9 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1396,10 +1347,9 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1412,10 +1362,9 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1428,10 +1377,9 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1444,10 +1392,9 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1460,10 +1407,9 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1476,10 +1422,9 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1492,10 +1437,9 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1508,10 +1452,9 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1524,10 +1467,9 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1540,10 +1482,9 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1556,10 +1497,9 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1572,10 +1512,9 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1588,10 +1527,9 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1604,10 +1542,9 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1620,10 +1557,9 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1636,10 +1572,9 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1652,10 +1587,9 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1668,10 +1602,9 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1684,10 +1617,9 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1700,10 +1632,9 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1716,10 +1647,9 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1732,10 +1662,9 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1748,10 +1677,9 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1764,10 +1692,9 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1780,10 +1707,9 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1796,10 +1722,9 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1812,10 +1737,9 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1828,10 +1752,9 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1844,10 +1767,9 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1860,10 +1782,9 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1876,10 +1797,9 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1892,10 +1812,9 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1908,10 +1827,9 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1924,10 +1842,9 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1940,10 +1857,9 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1956,10 +1872,9 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1972,10 +1887,9 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1988,10 +1902,9 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2004,10 +1917,9 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2020,10 +1932,9 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2036,10 +1947,9 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2052,10 +1962,9 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2068,10 +1977,9 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2084,10 +1992,9 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2100,10 +2007,9 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2116,10 +2022,9 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2132,10 +2037,9 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2148,10 +2052,9 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2164,10 +2067,9 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2180,10 +2082,9 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2196,10 +2097,9 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2212,10 +2112,9 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2228,10 +2127,9 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2244,10 +2142,9 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2260,10 +2157,9 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2276,10 +2172,9 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2292,10 +2187,9 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2308,10 +2202,9 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2324,10 +2217,9 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2340,10 +2232,9 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2356,10 +2247,9 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2372,10 +2262,9 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2388,10 +2277,9 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2404,10 +2292,9 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2420,10 +2307,9 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2436,10 +2322,9 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2452,10 +2337,9 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2468,10 +2352,9 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2484,10 +2367,9 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2500,10 +2382,9 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2516,10 +2397,9 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2532,10 +2412,9 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2548,10 +2427,9 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2564,10 +2442,9 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2580,10 +2457,9 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2596,10 +2472,9 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2612,10 +2487,9 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2628,10 +2502,9 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2644,10 +2517,9 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2660,10 +2532,9 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2676,10 +2547,9 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2692,10 +2562,9 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2708,10 +2577,9 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2724,10 +2592,9 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2740,10 +2607,9 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2756,10 +2622,9 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2772,10 +2637,9 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2788,10 +2652,9 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2804,10 +2667,9 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2820,10 +2682,9 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2836,10 +2697,9 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2852,10 +2712,9 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2868,10 +2727,9 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2884,10 +2742,9 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2900,10 +2757,9 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2916,10 +2772,9 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2932,10 +2787,9 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2948,10 +2802,9 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2964,10 +2817,9 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2980,10 +2832,9 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2996,10 +2847,9 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -3012,10 +2862,9 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3028,10 +2877,9 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3044,10 +2892,9 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3060,10 +2907,9 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -3076,10 +2922,9 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -3092,10 +2937,9 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -3108,10 +2952,9 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -3124,10 +2967,9 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -3140,10 +2982,9 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -3156,10 +2997,9 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -3172,10 +3012,9 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -3188,10 +3027,9 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -3204,10 +3042,9 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -3220,10 +3057,9 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -3236,10 +3072,9 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -3252,10 +3087,9 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -3268,10 +3102,9 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -3284,10 +3117,9 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -3300,10 +3132,9 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -3316,10 +3147,9 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -3332,10 +3162,9 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -3348,10 +3177,9 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -3364,10 +3192,9 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -3380,10 +3207,9 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -3396,10 +3222,9 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -3412,10 +3237,9 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -3428,10 +3252,9 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -3444,10 +3267,9 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -3460,10 +3282,9 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -3476,10 +3297,9 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -3492,10 +3312,9 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -3508,10 +3327,9 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -3524,10 +3342,9 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -3540,10 +3357,9 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -3556,10 +3372,9 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -3572,10 +3387,9 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -3588,10 +3402,9 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -3604,10 +3417,9 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -3620,10 +3432,9 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -3636,10 +3447,9 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -3652,10 +3462,9 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -3668,10 +3477,9 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -3684,10 +3492,9 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -3700,10 +3507,9 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -3716,10 +3522,9 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -3732,10 +3537,9 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -3748,10 +3552,9 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -3764,10 +3567,9 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -3780,10 +3582,9 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -3796,10 +3597,9 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -3812,10 +3612,9 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -3828,10 +3627,9 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -3844,10 +3642,9 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -3860,10 +3657,9 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -3876,10 +3672,9 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -3892,10 +3687,9 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -3908,10 +3702,9 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -3924,10 +3717,9 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -3940,10 +3732,9 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -3956,10 +3747,9 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -3972,10 +3762,9 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -3988,10 +3777,9 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -4004,10 +3792,9 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -4020,10 +3807,9 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -4036,10 +3822,9 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -4052,10 +3837,9 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -4068,10 +3852,9 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -4084,10 +3867,9 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -4100,10 +3882,9 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -4116,10 +3897,9 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -4132,10 +3912,9 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -4148,10 +3927,9 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -4164,10 +3942,9 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -4180,10 +3957,9 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -4196,10 +3972,9 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -4212,10 +3987,9 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -4228,10 +4002,9 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -4244,10 +4017,9 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -4260,10 +4032,9 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -4276,10 +4047,9 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -4292,10 +4062,9 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -4308,10 +4077,9 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -4324,10 +4092,9 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -4340,10 +4107,9 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -4356,10 +4122,9 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -4372,10 +4137,9 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -4388,10 +4152,9 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -4404,10 +4167,9 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -4420,10 +4182,9 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -4436,10 +4197,9 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -4452,10 +4212,9 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -4468,10 +4227,9 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -4484,10 +4242,9 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -4500,10 +4257,9 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -4516,10 +4272,9 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -4532,10 +4287,9 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -4548,10 +4302,9 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -4564,10 +4317,9 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -4580,10 +4332,9 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -4596,10 +4347,9 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -4612,10 +4362,9 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -4628,10 +4377,9 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -4644,10 +4392,9 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -4660,10 +4407,9 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -4676,10 +4422,9 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -4692,10 +4437,9 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -4708,10 +4452,9 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -4724,10 +4467,9 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -4740,10 +4482,9 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -4756,10 +4497,9 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -4772,10 +4512,9 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -4788,10 +4527,9 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -4804,10 +4542,9 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -4820,10 +4557,9 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -4836,10 +4572,9 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -4852,10 +4587,9 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -4868,10 +4602,9 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -4884,10 +4617,9 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -4900,10 +4632,9 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -4916,10 +4647,9 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -4932,10 +4662,9 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -4948,10 +4677,9 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -4964,10 +4692,9 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -4980,10 +4707,9 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -4996,10 +4722,9 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -5012,10 +4737,9 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -5028,10 +4752,9 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -5044,10 +4767,9 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -5060,10 +4782,9 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -5076,10 +4797,9 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -5092,10 +4812,9 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -5108,10 +4827,9 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -5124,10 +4842,9 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -5140,10 +4857,9 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -5156,10 +4872,9 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -5172,10 +4887,9 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -5188,10 +4902,9 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -5204,10 +4917,9 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -5220,10 +4932,9 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -5236,10 +4947,9 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -5252,10 +4962,9 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -5268,10 +4977,9 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -5284,10 +4992,9 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -5300,10 +5007,9 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -5316,10 +5022,9 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -5332,10 +5037,9 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -5348,10 +5052,9 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -5364,10 +5067,9 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -5380,10 +5082,9 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -5396,10 +5097,9 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -5412,10 +5112,9 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -5428,10 +5127,9 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -5444,10 +5142,9 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -5460,10 +5157,9 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -5476,10 +5172,9 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -5492,10 +5187,9 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -5508,10 +5202,9 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -5524,10 +5217,9 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -5540,10 +5232,9 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -5556,10 +5247,9 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -5572,10 +5262,9 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -5588,10 +5277,9 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -5604,10 +5292,9 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -5620,10 +5307,9 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -5636,10 +5322,9 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -5652,10 +5337,9 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -5668,10 +5352,9 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -5684,10 +5367,9 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -5700,10 +5382,9 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -5716,10 +5397,9 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -5732,10 +5412,9 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -5748,10 +5427,9 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -5764,10 +5442,9 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -5780,10 +5457,9 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -5796,10 +5472,9 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -5812,10 +5487,9 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -5828,10 +5502,9 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -5844,10 +5517,9 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -5860,10 +5532,9 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -5876,10 +5547,9 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -5892,10 +5562,9 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -5908,10 +5577,9 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -5924,10 +5592,9 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -5940,10 +5607,9 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -5956,10 +5622,9 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -5972,10 +5637,9 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -5988,10 +5652,9 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -6004,10 +5667,9 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -6020,10 +5682,9 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -6036,10 +5697,9 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -6052,10 +5712,9 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -6068,10 +5727,9 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -6084,10 +5742,9 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -6100,10 +5757,9 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -6116,10 +5772,9 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -6132,10 +5787,9 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -6148,10 +5802,9 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -6164,10 +5817,9 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -6180,10 +5832,9 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -6196,10 +5847,9 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -6212,10 +5862,9 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -6228,10 +5877,9 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -6244,10 +5892,9 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -6260,10 +5907,9 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -6276,10 +5922,9 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -6292,10 +5937,9 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -6308,10 +5952,9 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -6324,10 +5967,9 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Pro (locked after 14 days)</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr"/>
+          <t>Yes, unlimited</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6384,7 +6026,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Poses 1 to 14 are what every Free user sees first.</t>
+          <t>Every pose is free to do, every day, forever. Only viewing photos older than 14 days is Pro.</t>
         </is>
       </c>
     </row>

--- a/final-plan/Final-Plan-Pose-List.xlsx
+++ b/final-plan/Final-Plan-Pose-List.xlsx
@@ -615,6 +615,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -630,6 +631,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -645,6 +647,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -660,6 +663,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -675,6 +679,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -690,6 +695,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -705,6 +711,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -712,7 +719,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lean in super close</t>
+          <t>Selfie as if you're saying "wait for me" without words</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -720,6 +727,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -727,7 +735,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Look like you're about to say something</t>
+          <t>Selfie in the face you make when you're being watched</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -735,6 +743,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -742,7 +751,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a fish</t>
+          <t>Selfie pretending you're waiting for a text back</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -750,6 +759,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -757,7 +767,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you hear good news</t>
+          <t>Mid-yawn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -765,6 +775,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -772,7 +783,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Selfie as if you're meeting yourself for the first time</t>
+          <t>Half laugh, half cringe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -780,6 +791,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -787,7 +799,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pinch your own nose</t>
+          <t>Recreate your Pose 1 selfie</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -795,6 +807,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -802,7 +815,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Look over your shoulder</t>
+          <t>Selfie pretending you're a bunny</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -810,6 +823,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -817,7 +831,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Selfie pretending you've got all the time in the world</t>
+          <t>Side profile, looking away</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -825,6 +839,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -832,7 +847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're surprised</t>
+          <t>Selfie leaning back as far as you can</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -840,6 +855,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -847,7 +863,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Selfie as if you're about to kiss the camera</t>
+          <t>Selfie with your mouth in an "O"</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -855,6 +871,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -862,7 +879,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Selfie with your head resting on your arm</t>
+          <t>Selfie as if you can't believe what you just saw</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -870,6 +887,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -877,7 +895,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Look down at the camera</t>
+          <t>Blow a kiss</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -885,6 +903,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -892,7 +911,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a judge</t>
+          <t>Cross your fingers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -900,6 +919,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -907,7 +927,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're stuck in traffic</t>
+          <t>Selfie pretending you're reading a message that made you smile</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -915,6 +935,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -922,7 +943,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "you're so lucky to have me" without words</t>
+          <t>Dramatic side-eye</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -930,6 +951,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -937,7 +959,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Confused face</t>
+          <t>Selfie with your cheeks sucked in</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -945,6 +967,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -952,7 +975,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Look jealous</t>
+          <t>Selfie as if you're saying "you're so lucky to have me" without words</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -960,6 +983,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -967,7 +991,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Selfie pretending you've just woken up</t>
+          <t>Selfie in the face you make when you can't stop smiling</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -975,6 +999,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -982,7 +1007,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're in love</t>
+          <t>Selfie pretending you're boiling hot</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -990,6 +1015,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -997,7 +1023,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "you're in so much trouble" without words</t>
+          <t>Selfie pretending you're reacting to a terrible pun</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1005,6 +1031,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1012,7 +1039,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Innocent angel face</t>
+          <t>Selfie mid-jump</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1020,6 +1047,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1027,7 +1055,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Look like you have a brilliant idea</t>
+          <t>Selfie pretending you're a ninja</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1035,6 +1063,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1042,7 +1071,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Selfie pretending it's the best day ever</t>
+          <t>Duck face</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1050,6 +1079,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1057,7 +1087,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you hear bad news</t>
+          <t>Pretend to check a watch on your wrist</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1065,6 +1095,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1072,7 +1103,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "come here" without words</t>
+          <t>Hand dramatically across your forehead</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1080,6 +1111,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1087,7 +1119,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Selfie where the left half is happy and the right half is grumpy</t>
+          <t>Selfie with your "I'm not even mad" face</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1095,6 +1127,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1102,7 +1135,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Look at the camera like you miss someone</t>
+          <t>Eyebrow wiggle</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1110,6 +1143,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1117,7 +1151,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Selfie pretending you've just won the lottery</t>
+          <t>Selfie as if your partner is standing right behind you</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1125,6 +1159,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1132,7 +1167,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you win an argument</t>
+          <t>Selfie pretending you're underwater</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1140,6 +1175,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1147,7 +1183,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Selfie as if it's the final scene of the film</t>
+          <t>Selfie in the face you make when you want to be left alone</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1155,6 +1191,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1162,7 +1199,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sour face, like you bit a lemon</t>
+          <t>Cheeky grin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1170,6 +1207,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1177,7 +1215,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Look up at the camera</t>
+          <t>Hold the phone as far away as you can</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1185,6 +1223,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1192,7 +1231,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Selfie pretending you're accepting an award</t>
+          <t>Selfie pretending you're asleep</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1200,6 +1239,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1207,7 +1247,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're hungry</t>
+          <t>Selfie with your tongue sticking out sideways</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1215,6 +1255,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1222,7 +1263,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "I can't wait to see you" without words</t>
+          <t>Selfie as if you've just walked into the room</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1230,6 +1271,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1237,7 +1279,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Selfie from a doorway</t>
+          <t>Rock-on hand</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1245,6 +1287,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1252,7 +1295,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Look totally bored</t>
+          <t>Selfie with one eyebrow up, one down</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1260,6 +1303,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1267,7 +1311,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a cat</t>
+          <t>Selfie as if you're saying "I told you so" without words</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1275,6 +1319,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1282,7 +1327,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you can't stop smiling</t>
+          <t>Selfie in the face you make when you're hungry</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1290,6 +1335,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1297,7 +1343,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Selfie as if you're about to hug the camera</t>
+          <t>Selfie with the phone sideways and your face filling the screen</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1305,6 +1351,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1312,7 +1359,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Selfie with your fingers pulling your eyes wide</t>
+          <t>Selfie pretending you're a news presenter</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1320,6 +1367,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1327,7 +1375,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Look like you just lost</t>
+          <t>Selfie with your head dropped forward, hair hanging</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1335,6 +1383,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1342,7 +1391,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a robot</t>
+          <t>Tongue caught between your teeth</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1350,6 +1399,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1357,7 +1407,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you lose an argument</t>
+          <t>Selfie pretending you've just woken up</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1365,6 +1415,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1372,7 +1423,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Selfie as if you can't believe what you just ate</t>
+          <t>Fake sneeze</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1380,6 +1431,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1387,7 +1439,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fake sneeze</t>
+          <t>Hands in prayer</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1395,6 +1447,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1402,7 +1455,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Look madly in love</t>
+          <t>Selfie with one eye wide, one eye squinted</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1410,6 +1463,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1417,7 +1471,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Selfie pretending you're at a wedding</t>
+          <t>Selfie as if you're saying "I'm so proud of you" without words</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1425,6 +1479,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1432,7 +1487,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you've made a mistake</t>
+          <t>Selfie in the face you make when you want a hug</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1440,6 +1495,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1447,7 +1503,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Selfie as if you can't believe what you just saw</t>
+          <t>Selfie whispering into the camera</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1455,6 +1511,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1462,7 +1519,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Selfie in your most mysterious pose</t>
+          <t>Selfie pretending you're a pirate</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1470,6 +1527,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1477,7 +1535,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Look at the camera like it's your favourite person</t>
+          <t>Selfie pretending you've just been told a joke</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1485,6 +1543,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1492,7 +1551,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Selfie pretending you're taking a bow</t>
+          <t>Pout</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1500,6 +1559,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1507,7 +1567,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're laughing too hard</t>
+          <t>Look like you've just been told off</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1515,6 +1575,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1522,7 +1583,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Selfie as if you've forgotten your lines</t>
+          <t>Selfie with your "I knew you'd say that" face</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1530,6 +1591,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1537,7 +1599,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fist pump</t>
+          <t>Salute</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1545,6 +1607,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1552,7 +1615,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Look like you're keeping a secret</t>
+          <t>Squint like a bright light just hit you</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1560,6 +1623,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1567,7 +1631,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Selfie pretending you're crying with happiness</t>
+          <t>Selfie as if you're saying "goodnight" without words</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1575,6 +1639,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1582,7 +1647,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you want a hug</t>
+          <t>Selfie pretending you're lifting something heavy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1590,6 +1655,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1597,7 +1663,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Selfie as if you've just said something silly</t>
+          <t>Selfie in the face you make when you're being teased</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1605,6 +1671,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1612,7 +1679,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Suspicious side-eye</t>
+          <t>Selfie pretending you're a lion</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1620,6 +1687,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1627,7 +1695,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Look like you just won</t>
+          <t>Selfie as if you have no idea the camera is on</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1635,6 +1703,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1642,7 +1711,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Selfie pretending you're the winner</t>
+          <t>Selfie pretending you're a cowboy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1650,6 +1719,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1657,7 +1727,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you can't decide</t>
+          <t>Selfie with your lips pushed to one side</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1665,6 +1735,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1672,7 +1743,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Selfie as if it's the first scene of the film</t>
+          <t>Selfie with your "we're definitely lost" face</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1680,6 +1751,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1687,7 +1759,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fake scream</t>
+          <t>Selfie as if you're about to cry and laugh at once</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1695,6 +1767,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1702,7 +1775,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Look at the camera like you're a detective</t>
+          <t>Selfie pretending you've just seen a spider</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1710,6 +1783,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1717,7 +1791,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Selfie pretending you're in a fight</t>
+          <t>Make a triangle with your hands</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1725,6 +1799,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1732,7 +1807,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're being teased</t>
+          <t>Squish your cheeks together</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1740,6 +1815,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1747,7 +1823,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Selfie as if you've been waiting forever</t>
+          <t>Hair covering one eye</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1755,6 +1831,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1762,7 +1839,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Selfie with your tongue sticking out sideways</t>
+          <t>Selfie as if you're saying "good morning" without words</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1770,6 +1847,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1777,7 +1855,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Look at the camera like it owes you money</t>
+          <t>Camera held below your chin</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1785,6 +1863,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1792,7 +1871,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Selfie pretending you're in a music video</t>
+          <t>Selfie in the face you make when you hear bad news</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1800,6 +1879,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1807,7 +1887,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're embarrassed</t>
+          <t>Smile with no teeth</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1815,6 +1895,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1822,7 +1903,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Selfie as if you're accepting a dare</t>
+          <t>Selfie as if you're the main character</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1830,6 +1911,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1837,7 +1919,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Selfie with one eye wide, one eye squinted</t>
+          <t>One hand behind your head</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -1845,6 +1927,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1852,7 +1935,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Look like you heard a strange noise</t>
+          <t>Squint like you can't see anything</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -1860,6 +1943,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1867,7 +1951,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a monkey</t>
+          <t>Selfie as if you're saying "I love you" without words</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -1875,6 +1959,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1882,7 +1967,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're lying</t>
+          <t>Selfie leaning against a wall</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -1890,6 +1975,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1897,7 +1983,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "I told you so" without words</t>
+          <t>Selfie pretending you're a vampire</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -1905,6 +1991,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1912,7 +1999,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Evil grin</t>
+          <t>Selfie with your teeth showing, no smile</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -1920,6 +2007,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1927,7 +2015,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Look impressed</t>
+          <t>Pretend to brush dirt off your shoulder</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -1935,6 +2023,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1942,7 +2031,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a villain</t>
+          <t>Selfie as if you're counting down 3, 2, 1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -1950,6 +2039,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1957,7 +2047,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're tired</t>
+          <t>Selfie copying your partner's usual face</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -1965,6 +2055,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1972,7 +2063,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Selfie as if you're thinking of your partner right now</t>
+          <t>Look left, then right, then at the camera</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -1980,6 +2071,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -1987,7 +2079,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Hands clasped, begging</t>
+          <t>Selfie pretending you're a ghost</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -1995,6 +2087,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2002,7 +2095,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Look like you're trying not to laugh</t>
+          <t>Goofy buck-teeth face</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2010,6 +2103,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2017,7 +2111,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Selfie pretending you're asleep</t>
+          <t>Look over your shoulder</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2025,6 +2119,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2032,7 +2127,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you want to be left alone</t>
+          <t>Two peace signs</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2040,6 +2135,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2047,7 +2143,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "you're the best" without words</t>
+          <t>Selfie as if you're saying "I'm sorry" without words</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2055,6 +2151,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2062,7 +2159,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Caught mid-laugh</t>
+          <t>Selfie in the face you make when you can't decide</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2070,6 +2167,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2077,7 +2175,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Look like you forgot something important</t>
+          <t>Look at the camera like you're flirting</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2085,6 +2183,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2092,7 +2191,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a spy</t>
+          <t>Selfie pretending you're a judge</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2100,6 +2199,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2107,7 +2207,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're being watched</t>
+          <t>Selfie with your top lip over your teeth</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2115,6 +2215,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2122,7 +2223,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "I'm hungry" without words</t>
+          <t>Selfie as if you're about to tell a long story</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2130,6 +2231,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2137,7 +2239,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Selfie with your head tilted and your eyes crossed</t>
+          <t>Selfie pretending you're in a lift with a stranger</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2145,6 +2247,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2152,7 +2255,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Look like you're deep in thought</t>
+          <t>Selfie with your eyes crossed</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2160,6 +2263,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2167,7 +2271,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Selfie pretending you're guilty</t>
+          <t>Peek through your fingers</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2175,6 +2279,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2182,7 +2287,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're proud</t>
+          <t>Pretend to push the camera away</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2190,6 +2295,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2197,7 +2303,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Selfie as if you're leaving the room forever</t>
+          <t>Selfie in the pose your partner would pick for you</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2205,6 +2311,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2212,7 +2319,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Selfie with a tiny smile and big eyes</t>
+          <t>Selfie where the left half is happy and the right half is grumpy</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2220,6 +2327,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2227,7 +2335,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Look like you just remembered something</t>
+          <t>Selfie with your fingers pulling your mouth wide</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2235,6 +2343,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2242,7 +2351,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a lion</t>
+          <t>Selfie mid-spin</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2250,6 +2359,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2257,7 +2367,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Selfie in the face you make when you're annoyed</t>
+          <t>Selfie pretending you're a king or queen</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2265,6 +2375,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2272,7 +2383,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "goodnight" without words</t>
+          <t>Selfie in the face you make when you're in love</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2280,6 +2391,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2287,7 +2399,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mid-yawn</t>
+          <t>Selfie pretending you're waiting for water to boil</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2295,6 +2407,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2302,7 +2415,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Look super cool</t>
+          <t>Hair stuck straight up</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2310,6 +2423,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2317,7 +2431,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Selfie pretending you're floating</t>
+          <t>Selfie with your "I'll do it tomorrow" smile</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2325,6 +2439,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2332,7 +2447,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "wait for me" without words</t>
+          <t>Pretend to lock your lips and throw away the key</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2340,6 +2455,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2347,7 +2463,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Selfie with a double chin on purpose</t>
+          <t>Selfie while stretching</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2355,6 +2471,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2362,7 +2479,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Look proud</t>
+          <t>Selfie pretending you're in a music video</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2370,6 +2487,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2377,7 +2495,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a pirate</t>
+          <t>Selfie in the face you make when you win an argument</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2385,6 +2503,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2392,7 +2511,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Selfie as if you're about to cry and laugh at once</t>
+          <t>Selfie as if it's the final scene of the film</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2400,6 +2519,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2407,7 +2527,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Air kiss to the side</t>
+          <t>Finger on your lips, "shh"</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2415,6 +2535,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2422,7 +2543,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Look at the camera like you're flirting</t>
+          <t>Selfie pretending the camera is a baby</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2430,6 +2551,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2437,7 +2559,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Selfie pretending you're squeezed into a tiny box</t>
+          <t>Selfie as if you're thinking of your partner right now</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2445,6 +2567,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2452,7 +2575,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Selfie as if you're trying very hard to look natural</t>
+          <t>Selfie in the face you make when you're stuck in traffic</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2460,6 +2583,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2467,7 +2591,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Make a triangle with your hands</t>
+          <t>Puppy eyes</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2475,6 +2599,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2482,7 +2607,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Look like you've been caught</t>
+          <t>Selfie sitting cross-legged</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2490,6 +2615,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2497,7 +2623,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Selfie pretending you're on a magazine cover</t>
+          <t>Tuck your hair behind one ear</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -2505,6 +2631,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2512,7 +2639,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Selfie as if you're about to tell a long story</t>
+          <t>Selfie as if you've just said something silly</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -2520,6 +2647,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2527,7 +2655,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Selfie with your lips tucked in</t>
+          <t>Hands clasped, begging</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2535,6 +2663,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2542,7 +2671,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Look at the camera like you're about to propose</t>
+          <t>Point at the camera</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -2550,6 +2679,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2557,7 +2687,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Selfie pretending you're blowing a bubble</t>
+          <t>Selfie pretending you're a zombie</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2565,6 +2695,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2572,7 +2703,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "thank you" without words</t>
+          <t>Selfie in the face you make when you've made a mistake</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2580,6 +2711,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2587,7 +2719,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Selfie with both hands pushing your cheeks up into a smile</t>
+          <t>Eyes as wide as they go</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2595,6 +2727,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2602,7 +2735,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Look nervous</t>
+          <t>Wipe a fake tear from your cheek</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2610,6 +2743,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2617,7 +2751,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a boss</t>
+          <t>Selfie as if you've been waiting forever</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2625,6 +2759,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2632,7 +2767,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "I love you" without words</t>
+          <t>Your best smile of the whole challenge</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -2640,6 +2775,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2647,7 +2783,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Selfie whispering into the camera</t>
+          <t>Half a heart with one hand</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -2655,6 +2791,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2662,7 +2799,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Look like you've just been told off</t>
+          <t>Selfie pretending you're meeting a celebrity</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -2670,6 +2807,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2677,7 +2815,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Selfie pretending you're giving a speech</t>
+          <t>Frame the camera with your fingers like a film director</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -2685,6 +2823,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2692,7 +2831,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Selfie as if you're counting down 3, 2, 1</t>
+          <t>Recreate your favourite pose so far</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -2700,6 +2839,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2707,7 +2847,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Make a heart with your thumbs and fingers</t>
+          <t>Mouth wide open in a silent "no way"</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -2715,6 +2855,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2722,7 +2863,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Selfie pretending you're boiling hot</t>
+          <t>Selfie pretending you're squeezed into a tiny box</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -2730,6 +2871,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2737,7 +2879,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Selfie as if you can't believe what you just heard</t>
+          <t>Two fingers pointing at your eyes, then at the camera</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -2745,6 +2887,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2752,7 +2895,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Smug face</t>
+          <t>Selfie pretending you're stuck on a very slow loading screen</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -2760,6 +2903,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2767,7 +2911,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Selfie pretending you've just been told a joke</t>
+          <t>Selfie with a different face for each half</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -2775,6 +2919,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2782,7 +2927,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Selfie as if you've just walked into the room</t>
+          <t>Pretend to be bald</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -2790,6 +2935,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2797,7 +2943,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Hands framing your face</t>
+          <t>Selfie with your fingers making a moustache</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -2805,6 +2951,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2812,7 +2959,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Selfie pretending you're reading a very long message</t>
+          <t>Frozen mid-sentence</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -2820,6 +2967,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2827,7 +2975,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Selfie as if you're sharing the best gossip</t>
+          <t>Selfie with your "I can hear you chewing" face</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -2835,6 +2983,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2842,7 +2991,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Pretend to be bald</t>
+          <t>Hide your face in your hands, peeking out</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -2850,6 +2999,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2857,7 +3007,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Selfie pretending the camera just told you a joke</t>
+          <t>Selfie with your chin on your shoulder</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -2865,6 +3015,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -2872,7 +3023,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Selfie as if you've just been surprised from behind</t>
+          <t>Selfie in the face you make when you're embarrassed</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -2880,6 +3031,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -2887,7 +3039,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Selfie with your fingers making a moustache</t>
+          <t>Make a phone with your hand and hold it to your ear</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -2895,6 +3047,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -2902,7 +3055,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a statue</t>
+          <t>Selfie pretending you're opera singing</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -2910,6 +3063,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -2917,7 +3071,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Selfie as if you have no idea the camera is on</t>
+          <t>Point at yourself</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -2925,6 +3079,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -2932,7 +3087,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Squish your cheeks together</t>
+          <t>Selfie as if you're saying "come here" without words</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -2940,6 +3095,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -2947,7 +3103,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Selfie pretending you're in a lift with a stranger</t>
+          <t>Pretend to hold a tiny person in your palm</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -2955,6 +3111,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -2962,7 +3119,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Selfie as if the camera is a secret</t>
+          <t>Selfie with your "I've got a surprise for you" face</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -2970,6 +3127,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -2977,7 +3135,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Kissy face</t>
+          <t>Selfie pretending you're a superhero</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -2985,6 +3143,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -2992,7 +3151,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Selfie pretending you're reading a message that made you angry</t>
+          <t>Selfie as if someone is tickling you</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3000,6 +3159,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -3007,7 +3167,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "good morning" without words</t>
+          <t>Selfie with your mind blown, hands bursting out from your head</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3015,6 +3175,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -3022,7 +3183,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tilt your head the other way</t>
+          <t>Selfie as if you're saying "you're the best" without words</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3030,6 +3191,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -3037,7 +3199,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a dog</t>
+          <t>Selfie in the face you make when you hear good news</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3045,6 +3207,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -3052,7 +3215,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Selfie as if you're the main character</t>
+          <t>Pucker up like you're trying to whistle</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3060,6 +3223,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -3067,7 +3231,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Finger on your lips, "shh"</t>
+          <t>Selfie pretending you're in a fight</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3075,6 +3239,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -3082,7 +3247,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Selfie pretending you're whispering a secret</t>
+          <t>Hold your hands up like you're surrendering</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3090,6 +3255,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -3097,7 +3263,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "I'm sorry" without words</t>
+          <t>Selfie in the face you make when you're lying</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3105,6 +3271,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -3112,7 +3279,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Thumbs up and a big grin</t>
+          <t>Selfie with a blink caught halfway</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3120,6 +3287,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -3127,7 +3295,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a zombie</t>
+          <t>Selfie pretending you're floating</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3135,6 +3303,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -3142,7 +3311,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Selfie as if you're saying "I'm so proud of you" without words</t>
+          <t>Pretend to zip your lips shut</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3150,6 +3319,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -3157,7 +3327,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Point at the camera</t>
+          <t>Look down at the camera</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -3165,6 +3335,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -3172,7 +3343,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Selfie pretending you're in trouble</t>
+          <t>A slow, long blink</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -3180,6 +3351,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -3187,7 +3359,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Selfie as if you're trying to look natural</t>
+          <t>Selfie with your "I didn't hear you" face</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -3195,6 +3367,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -3202,7 +3375,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Selfie mid-jump</t>
+          <t>Double thumbs up</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -3210,6 +3383,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -3217,7 +3391,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a ghost</t>
+          <t>Look at the camera like you miss someone</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -3225,6 +3399,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -3232,7 +3407,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Selfie as if you're daring someone else</t>
+          <t>Selfie in slow motion, mid-blink</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -3240,6 +3415,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -3247,7 +3423,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Recreate your Pose 1 selfie</t>
+          <t>Look like you're keeping a secret</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -3255,6 +3431,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -3262,7 +3439,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Selfie pretending you can't wake up</t>
+          <t>Confused face</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -3270,6 +3447,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -3277,7 +3455,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Selfie as if you've just been dared</t>
+          <t>Both hands behind your head, relaxed</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3285,6 +3463,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -3292,7 +3471,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Hair covering one eye</t>
+          <t>Selfie crouching low</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -3300,6 +3479,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -3307,7 +3487,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Selfie pretending you're in a hurry</t>
+          <t>Selfie pretending you're a spy</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -3315,6 +3495,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -3322,7 +3503,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Selfie as if you can't believe your luck</t>
+          <t>Selfie pretending you're running late</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -3330,6 +3511,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -3337,7 +3519,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Selfie sitting cross-legged</t>
+          <t>Unimpressed, flat mouth, eyebrows up</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -3345,6 +3527,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -3352,7 +3535,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Selfie pretending you've just seen a spider</t>
+          <t>Your funniest face of the whole challenge</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -3360,6 +3543,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -3367,7 +3551,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Eyes as wide as they go</t>
+          <t>Hands over both ears</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -3375,6 +3559,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -3382,7 +3567,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Selfie pretending you're catching a snowflake on your tongue</t>
+          <t>Sleepy eyes, half closed</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -3390,6 +3575,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -3397,7 +3583,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Hair flip</t>
+          <t>Fake scream</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -3405,6 +3591,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -3412,7 +3599,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a penguin</t>
+          <t>Shy smile, biting your lip</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -3420,6 +3607,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -3427,7 +3615,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Squint like you can't see anything</t>
+          <t>Selfie pretending you're stepping into freezing water</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -3435,6 +3623,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -3442,7 +3631,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a ninja</t>
+          <t>Deadpan, no expression at all</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -3450,6 +3639,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -3457,7 +3647,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Side profile, looking away</t>
+          <t>Look at the camera like you're about to propose</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -3465,6 +3655,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -3472,7 +3663,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Selfie pretending you're at a first date</t>
+          <t>Selfie pretending you're in a movie trailer</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -3480,6 +3671,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -3487,7 +3679,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Selfie in your most innocent pose</t>
+          <t>Hands framing your face</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -3495,6 +3687,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -3502,7 +3695,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Selfie pretending you're innocent</t>
+          <t>Look like you're about to say something</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -3510,6 +3703,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -3517,7 +3711,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Shrug with both hands up</t>
+          <t>Hold your palm up to the camera: "talk to the hand"</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -3525,6 +3719,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -3532,7 +3727,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a superhero</t>
+          <t>Selfie pretending you're singing badly</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -3540,6 +3735,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -3547,7 +3743,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Selfie lying on your side</t>
+          <t>Smug face</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -3555,6 +3751,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -3562,7 +3759,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Selfie pretending you're running late</t>
+          <t>Slow clap</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -3570,6 +3767,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -3577,7 +3775,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Run both hands through your hair</t>
+          <t>Selfie pretending you're in a wildlife documentary</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -3585,6 +3783,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -3592,7 +3791,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a king or queen</t>
+          <t>Selfie with your "who ate the last one?" face</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -3600,6 +3799,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -3607,7 +3807,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Selfie with your whole face squished to one side</t>
+          <t>Hair flip</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -3615,6 +3815,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -3622,7 +3823,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Selfie pretending you're opera singing</t>
+          <t>Selfie pretending you're rapping</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -3630,6 +3831,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -3637,7 +3839,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Selfie crouching low</t>
+          <t>Wave at the camera</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -3645,6 +3847,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -3652,7 +3855,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Selfie pretending you're strong, flexing</t>
+          <t>Selfie with a double chin on purpose</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -3660,6 +3863,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -3667,7 +3871,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Hands over both ears</t>
+          <t>Selfie smiling politely at food you secretly hate</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -3675,6 +3879,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -3682,7 +3887,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Selfie pretending you're listening to something hilarious</t>
+          <t>"Who, me?" with a hand on your chest</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -3690,6 +3895,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -3697,7 +3903,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Make a phone with your hand and hold it to your ear</t>
+          <t>Selfie pretending you're on hold on the phone</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -3705,6 +3911,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -3712,7 +3919,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a teacher</t>
+          <t>Suspicious side-eye</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -3720,6 +3927,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -3727,7 +3935,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Selfie with a different face for each half</t>
+          <t>Selfie pretending you're a dog</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -3735,6 +3943,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -3742,7 +3951,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Selfie pretending you've just been proposed to</t>
+          <t>Selfie with your "it's fine" face (it is not fine)</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -3750,6 +3959,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -3757,7 +3967,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Make glasses with your fingers</t>
+          <t>Kiss your own fingertips like a chef</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -3765,6 +3975,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -3772,7 +3983,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Selfie pretending you're listening to something sad</t>
+          <t>Selfie where the left half is sleepy and the right half is shocked</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -3780,6 +3991,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -3787,7 +3999,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Selfie in your most romantic pose</t>
+          <t>Selfie pretending you're hearing the same joke for the hundredth time</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -3795,6 +4007,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -3802,7 +4015,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Selfie pretending you're freezing</t>
+          <t>Look at the camera like it owes you money</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -3810,6 +4023,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -3817,7 +4031,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Selfie with your head tilted back, laughing</t>
+          <t>Selfie with the biggest expression possible</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -3825,6 +4039,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -3832,7 +4047,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a news presenter</t>
+          <t>Make glasses with your fingers</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -3840,6 +4055,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -3847,7 +4063,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Selfie with your mouth stretched wide</t>
+          <t>Selfie pretending you're hiding from your partner</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -3855,6 +4071,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -3862,7 +4079,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a footballer who just scored</t>
+          <t>Selfie in the face you make when you're laughing too hard</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -3870,6 +4087,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -3877,7 +4095,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Selfie with your fingers pulling your eyes narrow</t>
+          <t>Look like you forgot something important</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -3885,6 +4103,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -3892,7 +4111,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Selfie pretending you're in a movie trailer</t>
+          <t>Selfie pretending you're a robot</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -3900,6 +4119,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -3907,7 +4127,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Your best smile of the whole challenge</t>
+          <t>Hands over both eyes</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -3915,6 +4135,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -3922,7 +4143,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Selfie pretending you're lifting something heavy</t>
+          <t>Selfie in your partner's favourite expression of yours</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -3930,6 +4151,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -3937,7 +4159,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Selfie upside down</t>
+          <t>Selfie pretending you're meeting their parents</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -3945,6 +4167,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -3952,7 +4175,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Selfie pretending you're meeting their parents</t>
+          <t>Pull your cheeks outward</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -3960,6 +4183,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -3967,7 +4191,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Selfie with your teeth showing, no smile</t>
+          <t>Selfie while walking toward the camera</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -3975,6 +4199,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -3982,7 +4207,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Selfie pretending you're on a rollercoaster</t>
+          <t>Make a heart with your thumbs and fingers</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -3990,6 +4215,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -3997,7 +4223,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Selfie with your fingers pulling your mouth wide</t>
+          <t>Selfie pretending you've just been given terrible advice</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -4005,6 +4231,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -4012,7 +4239,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Selfie pretending you're hiding from your partner</t>
+          <t>Selfie in your most confident pose</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -4020,6 +4247,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -4027,7 +4255,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Disgusted face, like you smelled something awful</t>
+          <t>Selfie as if you're about to kiss the camera</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -4035,6 +4263,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -4042,7 +4271,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Selfie pretending you're rapping</t>
+          <t>Selfie pretending you're in a strong wind</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -4050,6 +4279,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -4057,7 +4287,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tuck your hair behind one ear</t>
+          <t>Selfie with your eyes closed, peaceful</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -4065,6 +4295,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -4072,7 +4303,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a pop star</t>
+          <t>Dreamy smile, gazing at the ceiling</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -4080,6 +4311,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -4087,7 +4319,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Selfie with the biggest expression possible</t>
+          <t>Selfie smelling something delicious</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -4095,6 +4327,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -4102,7 +4335,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a movie star</t>
+          <t>Shrug with both hands up</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -4110,6 +4343,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -4117,7 +4351,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Hand in your hair</t>
+          <t>Look at the camera like you're a detective</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -4125,6 +4359,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -4132,7 +4367,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Selfie pretending you're reading a message that made you smile</t>
+          <t>Selfie pretending you're a cat</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -4140,6 +4375,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -4147,7 +4383,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Selfie with your eyebrows both down</t>
+          <t>Selfie after running on the spot for 10 seconds</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -4155,6 +4391,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -4162,7 +4399,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Selfie pretending you're on a secret mission</t>
+          <t>Hand on your heart</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -4170,6 +4407,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -4177,7 +4415,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Hand dramatically across your forehead</t>
+          <t>Selfie pretending you're at a first date</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -4185,6 +4423,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -4192,7 +4431,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Selfie pretending you're waiting for a text back</t>
+          <t>Selfie as if you've just been surprised from behind</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -4200,6 +4439,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -4207,7 +4447,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Your funniest face of the whole challenge</t>
+          <t>Selfie holding your breath</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -4215,6 +4455,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -4222,7 +4463,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Selfie pretending you're in a strong wind</t>
+          <t>Selfie in your most romantic pose</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -4230,6 +4471,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -4237,7 +4479,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Selfie with your chin tucked into your neck</t>
+          <t>Thumbs up and a big grin</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -4245,6 +4487,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -4252,7 +4495,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Selfie pretending you're the loser</t>
+          <t>Roll your eyes</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -4260,6 +4503,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -4267,7 +4511,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Selfie copying your partner's usual face</t>
+          <t>Selfie pretending you're blowing out candles</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -4275,6 +4519,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -4282,7 +4527,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Selfie pretending you're underwater</t>
+          <t>Selfie pretending you're catching a snowflake on your tongue</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -4290,6 +4535,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -4297,7 +4543,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Tilt your head as far as it goes</t>
+          <t>Camera held high above your head</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -4305,6 +4551,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -4312,7 +4559,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a cowboy</t>
+          <t>Selfie pretending you're taking a bow</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -4320,6 +4567,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -4327,7 +4575,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Selfie with your cheeks puffed and your eyes crossed</t>
+          <t>Selfie as if you're sharing the best gossip</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -4335,6 +4583,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -4342,7 +4591,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Selfie pretending you're sneaking around</t>
+          <t>Selfie pretending you're a fish</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -4350,6 +4599,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -4357,7 +4607,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Selfie with your eyes crossed</t>
+          <t>Selfie lying on your side</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -4365,6 +4615,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -4372,7 +4623,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Selfie pretending you're singing badly</t>
+          <t>Selfie as if you're trying very hard to look natural</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -4380,6 +4631,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -4387,7 +4639,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>One hand behind your head</t>
+          <t>Hang-loose hand</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -4395,6 +4647,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -4402,7 +4655,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a bunny</t>
+          <t>Selfie as if you're saying "thank you" without words</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -4410,6 +4663,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -4417,7 +4671,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Rock-on hand</t>
+          <t>Selfie pretending you're a statue</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -4425,6 +4679,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -4432,7 +4687,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Selfie pretending you're singing</t>
+          <t>Laugh with your eyes closed</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -4440,6 +4695,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -4447,7 +4703,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Deadpan, no expression at all</t>
+          <t>Selfie with your arm out like an aeroplane</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -4455,6 +4711,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -4462,7 +4719,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a model</t>
+          <t>Selfie with your "just one more episode" face</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -4470,6 +4727,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -4477,7 +4735,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Selfie while walking toward the camera</t>
+          <t>Selfie with your fingers framing a smile</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -4485,6 +4743,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -4492,7 +4751,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Selfie pretending you're blowing out candles</t>
+          <t>Selfie upside down</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -4500,6 +4759,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -4507,7 +4767,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Puppy eyes</t>
+          <t>Selfie pretending you're reading a message that made you angry</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -4515,6 +4775,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -4522,7 +4783,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Selfie pretending you're shouting</t>
+          <t>Selfie in your most elegant pose</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -4530,6 +4791,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -4537,7 +4799,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Hands in prayer</t>
+          <t>Selfie as if you're saying "you're in so much trouble" without words</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -4545,6 +4807,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -4552,7 +4815,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Selfie pretending you're listening to your favourite song</t>
+          <t>Look up at the camera</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -4560,6 +4823,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -4567,7 +4831,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Selfie with your eyes closed, peaceful</t>
+          <t>Excited bounce-up-and-down face</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -4575,6 +4839,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -4582,7 +4847,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a vampire</t>
+          <t>Selfie as if you're saying "I can't wait to see you" without words</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -4590,6 +4855,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -4597,7 +4863,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Pout</t>
+          <t>Pretend to pull the camera closer</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -4605,6 +4871,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -4612,7 +4879,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Selfie pretending the camera is a baby</t>
+          <t>Selfie pretending you've walked into your own surprise party</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -4620,6 +4887,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -4627,7 +4895,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Selfie leaning against a wall</t>
+          <t>Selfie with a tiny smile and big eyes</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -4635,6 +4903,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -4642,7 +4911,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a chef</t>
+          <t>Selfie pretending you're an excited puppy waiting for a walk</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -4650,6 +4919,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -4657,7 +4927,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Hair covering your whole face</t>
+          <t>Tilt your head as far as it goes</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -4665,6 +4935,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -4672,7 +4943,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Selfie pretending you're a mannequin</t>
+          <t>Hair covering your whole face</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -4680,6 +4951,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -4687,7 +4959,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Selfie in your partner's favourite expression of yours</t>
+          <t>Selfie pretending you're giving a speech</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -4695,6 +4967,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -4702,7 +4975,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Selfie with your mouth in an "O"</t>
+          <t>Selfie as if you're meeting yourself for the first time</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -4710,6 +4983,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -4717,7 +4991,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Selfie with your eyebrows both up</t>
+          <t>Tilt your head the other way</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -4725,6 +4999,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -4732,7 +5007,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Hand on your heart</t>
+          <t>Thumbs down with a big grin</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -4740,6 +5015,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -4747,7 +5023,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Part your hair down the middle with your fingers</t>
+          <t>Disgusted face, like you smelled something awful</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -4755,6 +5031,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -4762,7 +5039,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Selfie while walking away, looking back</t>
+          <t>Look like you're trying not to laugh</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -4770,6 +5047,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -4777,7 +5055,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Selfie with your lips pushed to one side</t>
+          <t>Fist pump</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -4785,6 +5063,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -4792,7 +5071,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Selfie with your top lip over your teeth</t>
+          <t>Look like you heard a strange noise</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -4800,6 +5079,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -4807,7 +5087,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Selfie in your most awkward pose</t>
+          <t>Selfie with your head resting on your arm</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -4815,6 +5095,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -4822,7 +5103,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Selfie where the left half is sleepy and the right half is shocked</t>
+          <t>Selfie pretending you're on a magazine cover</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -4830,6 +5111,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -4837,7 +5119,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Recreate your favourite pose so far</t>
+          <t>Tap your temple, "think about it"</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -4845,6 +5127,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -4852,7 +5135,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Hold your hands up like you're surrendering</t>
+          <t>Look like you have a brilliant idea</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -4860,6 +5143,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -4867,7 +5151,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Selfie in your most relaxed pose</t>
+          <t>Selfie in the pose you think your partner will do today</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -4875,6 +5159,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -4882,7 +5167,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Selfie after running on the spot for 10 seconds</t>
+          <t>Count to five on your fingers</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -4890,6 +5175,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -4897,7 +5183,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Hands over both eyes</t>
+          <t>Look like you've been caught</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -4905,6 +5191,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -4912,7 +5199,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Selfie in your most confident pose</t>
+          <t>Selfie with your lips tucked in</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -4920,6 +5207,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -4927,7 +5215,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Selfie while stretching</t>
+          <t>Selfie pretending you're holding in a sneeze</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -4935,6 +5223,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -4942,7 +5231,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Point at yourself</t>
+          <t>Heart made with both hands</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -4950,6 +5239,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -4957,7 +5247,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Selfie in slow motion, mid-blink</t>
+          <t>Big dramatic sigh</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -4965,6 +5255,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -4972,7 +5263,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Peek through your fingers</t>
+          <t>Selfie with the camera tilted, face straight</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -4980,6 +5271,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -4987,7 +5279,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Selfie with your cheeks sucked in</t>
+          <t>Selfie pretending to taste your partner's cooking and love it</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -4995,6 +5287,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -5002,7 +5295,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Sleepy eyes, half closed</t>
+          <t>Selfie with the smallest expression possible</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -5010,6 +5303,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -5017,7 +5311,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Blow a kiss</t>
+          <t>Hand on your chin, thinking</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -5025,6 +5319,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -5032,7 +5327,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Messy hair, shaken up</t>
+          <t>Selfie pretending you're blowing a bubble</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -5040,6 +5335,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -5047,7 +5343,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Selfie with your head resting on your knees</t>
+          <t>Selfie as if you're accepting a dare</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -5055,6 +5351,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -5062,7 +5359,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Both hands behind your head, relaxed</t>
+          <t>Selfie with your "five more minutes" face</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -5070,6 +5367,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -5077,7 +5375,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Selfie looking down at your own shoulder</t>
+          <t>Selfie pretending you're at a wedding</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -5085,6 +5383,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -5092,7 +5391,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Selfie with your chin on your shoulder</t>
+          <t>Selfie as if you're leaving the room forever</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -5100,6 +5399,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -5107,7 +5407,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Laugh with your eyes closed</t>
+          <t>Selfie with your "where are my keys?" face</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -5115,6 +5415,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -5122,7 +5423,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>"Who, me?" with a hand on your chest</t>
+          <t>Selfie pretending you're listening to something sad</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -5130,6 +5431,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -5137,7 +5439,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Hair stuck straight up</t>
+          <t>Selfie in your most dramatic pose</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -5145,6 +5447,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -5152,7 +5455,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Selfie with a big stretch and a yawn</t>
+          <t>Innocent angel face</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -5160,6 +5463,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -5167,7 +5471,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Selfie with your nose scrunched</t>
+          <t>Selfie pretending you're trying to look taller</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -5175,6 +5479,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -5182,7 +5487,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Cover one eye with your hand</t>
+          <t>Selfie in your most ridiculous pose</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -5190,6 +5495,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -5197,7 +5503,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Selfie in your most dramatic pose</t>
+          <t>Selfie in your most relaxed pose</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -5205,6 +5511,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -5212,7 +5519,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Two fingers pointing at your eyes, then at the camera</t>
+          <t>Selfie pretending you're at the top of a very tall slide</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -5220,6 +5527,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -5227,7 +5535,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Hand on your chin, thinking</t>
+          <t>Look super cool</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -5235,6 +5543,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -5242,7 +5551,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Camera held below your chin</t>
+          <t>Selfie with your "I'm sure it was here a second ago" face</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -5250,6 +5559,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -5257,7 +5567,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Hold the phone as far away as you can</t>
+          <t>Selfie pretending you're freezing</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -5265,6 +5575,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -5272,7 +5583,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Camera held high above your head</t>
+          <t>Selfie as if it's the first scene of the film</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -5280,6 +5591,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -5287,7 +5599,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Salute</t>
+          <t>Selfie with your "you're not going to believe this" face</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -5295,6 +5607,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -5302,7 +5615,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Selfie mid-spin</t>
+          <t>Selfie pretending your name was just called out in class</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -5310,6 +5623,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -5317,7 +5631,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Hands on both cheeks</t>
+          <t>Look impressed</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -5325,6 +5639,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -5332,7 +5647,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Selfie with your fingers framing a smile</t>
+          <t>Fake crying face</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -5340,6 +5655,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -5347,7 +5663,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Selfie with the camera tilted, face straight</t>
+          <t>Sour face, like you bit a lemon</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -5355,6 +5671,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -5362,7 +5679,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Double thumbs up</t>
+          <t>Selfie from a doorway</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -5370,6 +5687,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -5377,7 +5695,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Pull your cheeks outward</t>
+          <t>Selfie pretending you're listening to your favourite song</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -5385,6 +5703,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -5392,7 +5711,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Selfie with one eyebrow up, one down</t>
+          <t>Arms crossed, serious face</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -5400,6 +5719,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -5407,7 +5727,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Selfie sitting on the floor</t>
+          <t>Look up at your own forehead</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -5415,6 +5735,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -5422,7 +5743,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Selfie in your most ridiculous pose</t>
+          <t>Selfie pretending you're reading a very long message</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -5430,6 +5751,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -5437,7 +5759,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Selfie in the pose you think your partner will do today</t>
+          <t>Selfie as if you've forgotten your lines</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -5445,6 +5767,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -5452,7 +5775,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Selfie with only your top lip curled</t>
+          <t>Point over your shoulder</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -5460,6 +5783,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -5467,7 +5791,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Smirk like you know a secret</t>
+          <t>Pinch your own nose</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -5475,6 +5799,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -5482,7 +5807,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fake crying face</t>
+          <t>Evil grin</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -5490,6 +5815,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -5497,7 +5823,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Selfie with your fingers pushing up your nose</t>
+          <t>Selfie pretending you're on a rollercoaster</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -5505,6 +5831,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -5512,7 +5839,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Selfie holding your breath</t>
+          <t>Look nervous</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -5520,6 +5847,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -5527,7 +5855,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Side profile, half smile</t>
+          <t>Selfie as if you can't believe what you just heard</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -5535,6 +5863,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -5542,7 +5871,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Selfie lying on your front, chin on your hands</t>
+          <t>Selfie pretending you're in a hurry</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -5550,6 +5879,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -5557,7 +5887,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Selfie in the pose your partner would pick for you</t>
+          <t>Lean in super close</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -5565,6 +5895,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -5572,7 +5903,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Cheeky grin</t>
+          <t>Look totally bored</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -5580,6 +5911,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -5587,7 +5919,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Selfie with the smallest expression possible</t>
+          <t>Selfie pretending you've just won the lottery</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -5595,6 +5927,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -5602,7 +5935,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Point over your shoulder</t>
+          <t>Selfie with your "that's my favourite song" face</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -5610,6 +5943,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -5617,7 +5951,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Half a heart with one hand</t>
+          <t>Selfie in your most mysterious pose</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -5625,6 +5959,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -5632,7 +5967,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Arms crossed, serious face</t>
+          <t>Selfie pretending you're in a staring contest</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -5640,6 +5975,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -5647,7 +5983,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Selfie with your mind blown, hands bursting out from your head</t>
+          <t>Selfie in your most awkward pose</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -5655,6 +5991,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -5662,7 +5999,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Selfie with your eyes closed, mouth open</t>
+          <t>Back of your head, then peek round</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -5670,6 +6007,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -5677,7 +6015,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Selfie on tiptoes</t>
+          <t>Look jealous</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -5685,6 +6023,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -5692,7 +6031,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Duck face</t>
+          <t>Selfie pretending you can't remember your password</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -5700,6 +6039,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -5707,7 +6047,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Selfie in your most elegant pose</t>
+          <t>Selfie with your "I'm trying to be quiet" face</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -5715,6 +6055,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -5722,7 +6063,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Camera held low, looking up your nose</t>
+          <t>Selfie with your nose scrunched</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -5730,6 +6071,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -5737,7 +6079,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Fake gasp</t>
+          <t>Selfie pretending you've got all the time in the world</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -5745,6 +6087,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -5752,7 +6095,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Hands over your mouth, eyes smiling</t>
+          <t>Selfie with your "I smelled that from here" face</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -5760,6 +6103,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -5767,7 +6111,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Back of your head, then peek round</t>
+          <t>Selfie with your shoulders shrugged up to your ears</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -5775,6 +6119,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -5782,7 +6127,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Selfie with the camera straight, face tilted</t>
+          <t>Selfie pretending you stepped in something wet in your socks</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -5790,6 +6135,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -5797,7 +6143,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Selfie with a blink caught halfway</t>
+          <t>"Mind your own business" glare</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -5805,6 +6151,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -5812,7 +6159,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Cross your fingers</t>
+          <t>Selfie pretending it's the best day ever</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -5820,6 +6167,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -5827,7 +6175,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Wave at the camera</t>
+          <t>Selfie pretending you're proud of a tiny achievement</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -5835,6 +6183,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -5842,7 +6191,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Dramatic side-eye</t>
+          <t>Selfie pretending you're strong, flexing</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -5850,6 +6199,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -5857,7 +6207,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Selfie with your lips pulled tight</t>
+          <t>Selfie pretending you're crying with happiness</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -5865,6 +6215,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -5872,7 +6223,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Heart made with both hands</t>
+          <t>Selfie pretending you're apologising with your whole body</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -5880,6 +6231,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -5887,7 +6239,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Two peace signs</t>
+          <t>Selfie pretending you've lost track of where you parked</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -5895,6 +6247,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -5910,6 +6263,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -5925,6 +6279,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -5940,6 +6295,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -5955,6 +6311,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -5970,6 +6327,7 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
+      <c r="D366" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5982,7 +6340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -6030,6 +6388,13 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Similar poses (winning, sleeping, animals, kissing and so on) are spread far apart.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/final-plan/Final-Plan-Pose-List.xlsx
+++ b/final-plan/Final-Plan-Pose-List.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lie flat on your back and take it looking up</t>
+          <t>Take a picture lying down on your back</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -615,7 +615,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -631,7 +630,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -647,7 +645,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -663,7 +660,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -679,7 +675,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -695,7 +690,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -711,7 +705,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -727,7 +720,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -743,7 +735,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -759,7 +750,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -775,7 +765,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -791,7 +780,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -807,7 +795,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -823,7 +810,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -839,7 +825,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -855,7 +840,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -871,7 +855,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -887,7 +870,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -903,7 +885,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -919,7 +900,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -935,7 +915,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -951,7 +930,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -967,7 +945,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -983,7 +960,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -999,7 +975,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1015,7 +990,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1031,7 +1005,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1047,7 +1020,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1063,7 +1035,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1079,7 +1050,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1095,7 +1065,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1111,7 +1080,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1127,7 +1095,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1143,7 +1110,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1159,7 +1125,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1175,7 +1140,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1191,7 +1155,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1207,7 +1170,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1223,7 +1185,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1239,7 +1200,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1255,7 +1215,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1271,7 +1230,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1287,7 +1245,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1303,7 +1260,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1319,7 +1275,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1335,7 +1290,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1351,7 +1305,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1367,7 +1320,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1383,7 +1335,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1399,7 +1350,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1415,7 +1365,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1431,7 +1380,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1447,7 +1395,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1463,7 +1410,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1479,7 +1425,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1495,7 +1440,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1511,7 +1455,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1527,7 +1470,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1543,7 +1485,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1559,7 +1500,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1575,7 +1515,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1591,7 +1530,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1607,7 +1545,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1623,7 +1560,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1639,7 +1575,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1655,7 +1590,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1671,7 +1605,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1687,7 +1620,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1703,7 +1635,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1719,7 +1650,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1735,7 +1665,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1751,7 +1680,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1767,7 +1695,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1783,7 +1710,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1799,7 +1725,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1815,7 +1740,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1831,7 +1755,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1847,7 +1770,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1863,7 +1785,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1879,7 +1800,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1895,7 +1815,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1911,7 +1830,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1927,7 +1845,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1943,7 +1860,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1959,7 +1875,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1975,7 +1890,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1991,7 +1905,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2007,7 +1920,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2023,7 +1935,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2039,7 +1950,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2055,7 +1965,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2071,7 +1980,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2087,7 +1995,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2103,7 +2010,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2119,7 +2025,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2135,7 +2040,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2151,7 +2055,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2167,7 +2070,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2183,7 +2085,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2199,7 +2100,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2215,7 +2115,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2231,7 +2130,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2247,7 +2145,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2263,7 +2160,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2279,7 +2175,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2295,7 +2190,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2311,7 +2205,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2327,7 +2220,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2343,7 +2235,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2359,7 +2250,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2375,7 +2265,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2391,7 +2280,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2407,7 +2295,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2423,7 +2310,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2439,7 +2325,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2455,7 +2340,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2471,7 +2355,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2487,7 +2370,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2503,7 +2385,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2519,7 +2400,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2535,7 +2415,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2551,7 +2430,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2567,7 +2445,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2583,7 +2460,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2599,7 +2475,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2615,7 +2490,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2631,7 +2505,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2647,7 +2520,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2663,7 +2535,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2679,7 +2550,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2695,7 +2565,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2711,7 +2580,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2727,7 +2595,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2743,7 +2610,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2759,7 +2625,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2775,7 +2640,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2791,7 +2655,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2807,7 +2670,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2823,7 +2685,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2839,7 +2700,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2855,7 +2715,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2871,7 +2730,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2887,7 +2745,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2903,7 +2760,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2919,7 +2775,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2935,7 +2790,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2951,7 +2805,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2967,7 +2820,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2983,7 +2835,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2999,7 +2850,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -3015,7 +2865,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3031,7 +2880,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3047,7 +2895,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3063,7 +2910,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -3079,7 +2925,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -3095,7 +2940,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -3111,7 +2955,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -3127,7 +2970,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -3143,7 +2985,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -3159,7 +3000,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -3175,7 +3015,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -3191,7 +3030,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -3207,7 +3045,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -3223,7 +3060,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -3239,7 +3075,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -3255,7 +3090,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -3271,7 +3105,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -3287,7 +3120,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -3303,7 +3135,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -3319,7 +3150,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -3335,7 +3165,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -3351,7 +3180,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -3367,7 +3195,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -3383,7 +3210,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -3399,7 +3225,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -3415,7 +3240,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -3431,7 +3255,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -3447,7 +3270,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -3463,7 +3285,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -3479,7 +3300,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -3495,7 +3315,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -3511,7 +3330,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -3527,7 +3345,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -3543,7 +3360,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -3559,7 +3375,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -3575,7 +3390,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -3591,7 +3405,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -3607,7 +3420,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -3623,7 +3435,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -3639,7 +3450,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -3655,7 +3465,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -3671,7 +3480,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -3687,7 +3495,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -3703,7 +3510,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -3719,7 +3525,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -3735,7 +3540,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -3751,7 +3555,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -3767,7 +3570,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -3783,7 +3585,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -3799,7 +3600,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -3815,7 +3615,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -3831,7 +3630,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -3847,7 +3645,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -3863,7 +3660,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -3879,7 +3675,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -3895,7 +3690,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -3911,7 +3705,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -3927,7 +3720,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -3943,7 +3735,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -3959,7 +3750,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -3975,7 +3765,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -3991,7 +3780,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -4007,7 +3795,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -4023,7 +3810,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -4039,7 +3825,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -4055,7 +3840,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -4071,7 +3855,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -4087,7 +3870,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -4103,7 +3885,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -4119,7 +3900,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -4135,7 +3915,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -4151,7 +3930,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -4167,7 +3945,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -4183,7 +3960,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -4199,7 +3975,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -4215,7 +3990,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -4231,7 +4005,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -4247,7 +4020,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -4263,7 +4035,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -4279,7 +4050,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -4295,7 +4065,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -4311,7 +4080,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -4327,7 +4095,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -4343,7 +4110,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -4359,7 +4125,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -4375,7 +4140,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -4391,7 +4155,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -4407,7 +4170,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -4423,7 +4185,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -4439,7 +4200,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -4455,7 +4215,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -4471,7 +4230,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -4487,7 +4245,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -4503,7 +4260,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -4519,7 +4275,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -4535,7 +4290,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -4551,7 +4305,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -4567,7 +4320,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -4583,7 +4335,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -4599,7 +4350,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -4615,7 +4365,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -4631,7 +4380,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -4647,7 +4395,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -4663,7 +4410,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -4679,7 +4425,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -4695,7 +4440,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -4711,7 +4455,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -4727,7 +4470,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -4743,7 +4485,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -4759,7 +4500,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -4775,7 +4515,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -4791,7 +4530,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -4807,7 +4545,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -4823,7 +4560,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -4839,7 +4575,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -4855,7 +4590,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -4871,7 +4605,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -4887,7 +4620,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -4903,7 +4635,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -4919,7 +4650,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -4935,7 +4665,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -4951,7 +4680,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -4967,7 +4695,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -4983,7 +4710,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -4999,7 +4725,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -5015,7 +4740,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -5031,7 +4755,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -5047,7 +4770,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -5063,7 +4785,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -5079,7 +4800,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -5095,7 +4815,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -5111,7 +4830,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -5127,7 +4845,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -5143,7 +4860,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -5159,7 +4875,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -5175,7 +4890,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -5191,7 +4905,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -5207,7 +4920,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -5223,7 +4935,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -5239,7 +4950,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -5255,7 +4965,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -5271,7 +4980,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -5287,7 +4995,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -5303,7 +5010,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -5319,7 +5025,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -5335,7 +5040,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -5351,7 +5055,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -5367,7 +5070,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -5383,7 +5085,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -5399,7 +5100,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -5415,7 +5115,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -5431,7 +5130,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -5447,7 +5145,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -5463,7 +5160,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -5479,7 +5175,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -5495,7 +5190,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -5511,7 +5205,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -5527,7 +5220,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -5543,7 +5235,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -5559,7 +5250,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -5575,7 +5265,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -5591,7 +5280,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -5607,7 +5295,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -5623,7 +5310,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -5639,7 +5325,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -5655,7 +5340,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -5671,7 +5355,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -5687,7 +5370,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -5703,7 +5385,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -5719,7 +5400,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -5735,7 +5415,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -5751,7 +5430,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -5767,7 +5445,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -5783,7 +5460,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -5799,7 +5475,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -5815,7 +5490,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -5831,7 +5505,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -5847,7 +5520,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -5863,7 +5535,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -5879,7 +5550,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -5895,7 +5565,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -5911,7 +5580,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -5927,7 +5595,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -5943,7 +5610,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -5959,7 +5625,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -5975,7 +5640,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -5991,7 +5655,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -6007,7 +5670,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -6023,7 +5685,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -6039,7 +5700,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -6055,7 +5715,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -6071,7 +5730,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -6087,7 +5745,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -6103,7 +5760,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -6119,7 +5775,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -6135,7 +5790,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -6151,7 +5805,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -6167,7 +5820,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -6183,7 +5835,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -6199,7 +5850,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -6215,7 +5865,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -6231,7 +5880,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -6247,7 +5895,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -6263,7 +5910,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -6279,7 +5925,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -6295,7 +5940,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -6311,7 +5955,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -6327,7 +5970,6 @@
           <t>Yes, unlimited</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
